--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000321</v>
       </c>
       <c r="B2" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000321</v>
       </c>
       <c r="B2" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000321</v>
       </c>
       <c r="B2" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000321</v>
       </c>
       <c r="B2" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000321</v>
       </c>
       <c r="B2" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000321</v>
       </c>
       <c r="B2" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48297-2025 artfynd.xlsx
+++ b/artfynd/A 48297-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129000323</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
